--- a/AAII_Financials/Yearly/STZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STZ_YR_FIN.xlsx
@@ -1017,7 +1017,7 @@
         <v>21300</v>
       </c>
       <c r="G14" s="3">
-        <v>88200</v>
+        <v>112400</v>
       </c>
       <c r="H14" s="3">
         <v>707700</v>
@@ -1362,7 +1362,7 @@
         <v>443600</v>
       </c>
       <c r="G22" s="3">
-        <v>422900</v>
+        <v>415900</v>
       </c>
       <c r="H22" s="3">
         <v>356400</v>
